--- a/results/tables/tableA7_crisis_type_heterogeneity.xlsx
+++ b/results/tables/tableA7_crisis_type_heterogeneity.xlsx
@@ -73,22 +73,22 @@
     <t>transformation</t>
   </si>
   <si>
-    <t>H4_crisis_type_disaster__crisis_disaster_lag0</t>
-  </si>
-  <si>
-    <t>H4_crisis_type_climate__crisis_climate_lag0</t>
-  </si>
-  <si>
-    <t>H4_crisis_type_conflict__crisis_conflict_lag0</t>
-  </si>
-  <si>
-    <t>H4_crisis_type_health__crisis_health_lag0</t>
-  </si>
-  <si>
-    <t>H4_crisis_type_food__crisis_food_lag0</t>
-  </si>
-  <si>
-    <t>H4_crisis_type_refugee__crisis_refugee_lag0</t>
+    <t>crisis_type_disaster__crisis_disaster_lag0</t>
+  </si>
+  <si>
+    <t>crisis_type_climate__crisis_climate_lag0</t>
+  </si>
+  <si>
+    <t>crisis_type_conflict__crisis_conflict_lag0</t>
+  </si>
+  <si>
+    <t>crisis_type_health__crisis_health_lag0</t>
+  </si>
+  <si>
+    <t>crisis_type_food__crisis_food_lag0</t>
+  </si>
+  <si>
+    <t>crisis_type_refugee__crisis_refugee_lag0</t>
   </si>
   <si>
     <t>ln_emergency_commitment_musd</t>
@@ -130,25 +130,25 @@
     <t>ln_gdppc;ln_population;log_bilateral_trade;ln_conflict_deaths;ln_disaster_affected</t>
   </si>
   <si>
-    <t>Emergency-ODA country-year panel, disaster-type crisis media only, complete cases</t>
-  </si>
-  <si>
-    <t>Emergency-ODA country-year panel, climate-type crisis media only, complete cases</t>
-  </si>
-  <si>
-    <t>Emergency-ODA country-year panel, conflict-type crisis media only, complete cases</t>
-  </si>
-  <si>
-    <t>Emergency-ODA country-year panel, health-type crisis media only, complete cases</t>
-  </si>
-  <si>
-    <t>Emergency-ODA country-year panel, food-type crisis media only, complete cases</t>
-  </si>
-  <si>
-    <t>Emergency-ODA country-year panel, refugee-type crisis media only, complete cases</t>
-  </si>
-  <si>
-    <t>contemporaneous (months 0-11 of the commitment year, k=-11..0)</t>
+    <t>Emergency-ODA country-year panel, disaster crisis media, complete cases</t>
+  </si>
+  <si>
+    <t>Emergency-ODA country-year panel, climate crisis media, complete cases</t>
+  </si>
+  <si>
+    <t>Emergency-ODA country-year panel, conflict crisis media, complete cases</t>
+  </si>
+  <si>
+    <t>Emergency-ODA country-year panel, health crisis media, complete cases</t>
+  </si>
+  <si>
+    <t>Emergency-ODA country-year panel, food crisis media, complete cases</t>
+  </si>
+  <si>
+    <t>Emergency-ODA country-year panel, refugee crisis media, complete cases</t>
+  </si>
+  <si>
+    <t>contemporaneous (months 0-11 of the commitment year)</t>
   </si>
   <si>
     <t>ln(x+1)</t>
